--- a/Pandas/Datasets/students_clean.xlsx
+++ b/Pandas/Datasets/students_clean.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,17 +486,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STU01919</t>
+          <t>STU01689</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Jeremiah</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Grimes</t>
+          <t xml:space="preserve">  Lawson</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -504,7 +504,9 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Grade 1</t>
@@ -512,50 +514,50 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>amanda.grimes785@outlook.com</t>
+          <t>jeremiahl40@gmail.com</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(95) 8857227</t>
+          <t>(97) 5072407</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>08-31-2019</t>
+          <t>2018-05-26</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3.21</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Mongu</t>
+          <t xml:space="preserve">Lusaka   </t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Mary Grimes</t>
+          <t>Christina Lawson</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>78.2</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STU02745</t>
+          <t>STU01110</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Jeffrey</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wise   </t>
+          <t xml:space="preserve">  Davis</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -564,64 +566,60 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>thomas_wise@gmail.com</t>
+          <t>jeffrey.davis931@yahoo.com</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>260970116159</t>
+          <t>+260-96-9072838</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2023/07/01</t>
+          <t>2020/09/18</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ndola   </t>
-        </is>
-      </c>
+        <v>1.52</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Michelle Wise</t>
+          <t>Morgan Davis</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>83.3</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STU02843</t>
+          <t>STU00282</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Christopher</t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -629,116 +627,112 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>christopher_brown@gmail.com</t>
+          <t>amanda.stone152@yahoo.com</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0962209692</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>27 Mar 2023</t>
-        </is>
-      </c>
+          <t>(96) 8304611</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>1.3</v>
+        <v>3.73</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>CHIPATA</t>
+          <t>Livingstone</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Vanessa Brown</t>
+          <t>Nicholas Stone</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>70.3</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STU00654</t>
+          <t>STU02825</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Sara</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Barnes</t>
+          <t>Gutierrez</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>sara.barnes700@outlook.com</t>
+          <t>jason.gutierrez701@outlook.com</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>+260-97-1390306</t>
+          <t>+260-97-6862340</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13 Dec 2018</t>
+          <t>03-22-2024</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2.23</v>
+        <v>2.82</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Chingola</t>
+          <t>lusaka</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve">William Barnes   </t>
+          <t>Grace Gutierrez</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>96.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STU03253</t>
+          <t>STU03699</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Williams   </t>
+          <t xml:space="preserve">Fletcher   </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -747,68 +741,68 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>erinw52@school.edu.zm</t>
+          <t>scott.fletcher629@gmail.com</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>260959255370</t>
+          <t>+260-95-4915203</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>09/05/2022</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>2.32</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>mansa</t>
+          <t xml:space="preserve">  SOLWEZI</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brian Williams   </t>
+          <t>Melissa  Fletcher</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>60.6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STU01689</t>
+          <t>STU02917</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Lawson</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>-5</v>
+        <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -817,50 +811,50 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jeremiahl40@gmail.com</t>
+          <t>josephw7@yahoo.com</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(97) 5072407</t>
+          <t>(97) 1508563</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2018-05-26</t>
+          <t>02/04/2021</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>2.72</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lusaka   </t>
+          <t>chipata</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Christina Lawson</t>
+          <t>Kayla Wilson</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>62.1</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STU01032</t>
+          <t>STU02843</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Loretta</t>
+          <t>Christopher</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Foster</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -869,59 +863,59 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>loretta_foster@gmail.com</t>
+          <t>christopher_brown@gmail.com</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>260974160580</t>
+          <t>0962209692</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10-23-2023</t>
+          <t>27 Mar 2023</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Solwezi</t>
+          <t>CHIPATA</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Juan Foster   </t>
+          <t>Vanessa Brown</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>99.7</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STU01514</t>
+          <t>STU00561</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t xml:space="preserve">  Marilyn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t xml:space="preserve">Becker   </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -929,58 +923,52 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>henry_lee@gmail.com</t>
+          <t>marilyn_becker@outlook.com</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0978851786</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2022-05-28</t>
-        </is>
-      </c>
+          <t>+260-95-9250481</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>1.98</v>
+        <v>3.96</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LUSAKA</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Denise Lee</t>
-        </is>
-      </c>
+          <t>kabwe</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>75.59999999999999</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STU03457</t>
+          <t>STU01895</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rebekah</t>
+          <t xml:space="preserve">Steven   </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -989,129 +977,125 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>rebekah.brown888@outlook.com</t>
+          <t>stevenw52@school.edu.zm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(97) 7134382</t>
+          <t>260957565368</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>06-15-2020</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3.72</v>
+        <v>2.07</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>chingola</t>
+          <t>Livingstone</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Kayla Brown</t>
+          <t xml:space="preserve">  Sean Williams</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>60.9</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STU03665</t>
+          <t>STU01078</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Tyrone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ramos</t>
+          <t>Dennis</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>maria_ramos@school.edu.zm</t>
+          <t>tyrone.dennis470@outlook.com</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0953022756</t>
+          <t>0979016612</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>11-12-2022</t>
+          <t>2021-03-19</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>CHINGOLA</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kimberly Ramos   </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Chingola   </t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>75.2</v>
+        <v>95.40000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STU03820</t>
+          <t>STU04665</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Zoe</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1120,91 +1104,91 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jason.may184@school.edu.zm</t>
+          <t>zoet9@gmail.com</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(96) 8241125</t>
+          <t>260964790292</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>02-15-2024</t>
+          <t>12 Feb 2018</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3.04</v>
+        <v>2.39</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lusaka   </t>
+          <t>Chipata</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Tara  May</t>
+          <t>Ryan Turner</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>90.5</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STU02596</t>
+          <t>STU03356</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  David</t>
+          <t>Christopher</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jacobson</t>
+          <t>Webb</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>david_jacobson@school.edu.zm</t>
+          <t>christopher.webb735@outlook.com</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>+260-95-8348268</t>
+          <t>0975718099</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>03 Apr 2023</t>
+          <t>27/01/2020</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3.99</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>MONGU</t>
+          <t>chingola</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Zachary Jacobson</t>
+          <t>Alexis Webb</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1212,17 +1196,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STU03913</t>
+          <t>STU00735</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Kevin</t>
+          <t xml:space="preserve">  Donna</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t xml:space="preserve">  Whitehead</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1231,59 +1215,59 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>kevinl33@outlook.com</t>
+          <t>donna_whitehead@gmail.com</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>+260-96-2128812</t>
+          <t>0963635975</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>23 Nov 2019</t>
+          <t>09/05/2024</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Ndola</t>
+          <t>chipata</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emily Lane   </t>
+          <t>Angela Whitehead</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>70.09999999999999</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STU04556</t>
+          <t>STU04713</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Douglas</t>
+          <t>Kathryn</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martinez   </t>
+          <t>Shields</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1292,55 +1276,59 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>douglasm94@yahoo.com</t>
+          <t>kathryns57@school.edu.zm</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0952684383</t>
+          <t>+260-97-2662290</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>22/12/2019</t>
+          <t>04/09/2020</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
+        <v>2.83</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Ndola</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Anita Martinez</t>
+          <t>Wesley  Shields</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>76.90000000000001</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STU01280</t>
+          <t>STU04520</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Adrian</t>
+          <t>Catherine</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Khan</t>
+          <t xml:space="preserve">Curtis   </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1349,120 +1337,120 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>adrian.khan609@gmail.com</t>
+          <t>catherine.curtis822@yahoo.com</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0977658917</t>
+          <t>(96) 3170103</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2022/06/15</t>
+          <t>22 Feb 2023</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>2.05</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>LIVINGSTONE</t>
+          <t>Mongu</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Christopher Khan</t>
+          <t>Robert Curtis</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>89.7</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STU00145</t>
+          <t>STU02367</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>William</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Shelton</t>
+          <t>Zuniga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>amanda_shelton@yahoo.com</t>
+          <t>williamz39@gmail.com</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(95) 6960666</t>
+          <t>(96) 9367470</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>07-03-2020</t>
+          <t>2023/01/15</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3.66</v>
+        <v>1.53</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Kabwe</t>
+          <t>Ndola</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Gabriella  Shelton</t>
+          <t>Ann Zuniga</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>62.1</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STU00172</t>
+          <t>STU04009</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Brent</t>
+          <t>Kathleen</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ramos</t>
+          <t>Cole</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1471,59 +1459,59 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>brent.ramos229@yahoo.com</t>
+          <t>kathleen.cole957@outlook.com</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0963246154</t>
+          <t>0957848571</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2023/03/19</t>
+          <t>2023/08/23</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>2.19</v>
+        <v>1.69</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>chipata</t>
+          <t>Chingola</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Anna Ramos</t>
+          <t xml:space="preserve">  Isaac Cole</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>84.59999999999999</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STU02686</t>
+          <t>STU01837</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Crystal</t>
+          <t>Paige</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cooper</t>
+          <t>Harper</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1532,55 +1520,55 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>Grade 2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>paigeh91@school.edu.zm</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>+260-95-8899713</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>05/09/2023</t>
-        </is>
-      </c>
+          <t>260963796316</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>2.95</v>
+        <v>3.39</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  KITWE</t>
+          <t>Chipata</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Cooper   </t>
+          <t>Shannon Harper</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>60.2</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STU03756</t>
+          <t>STU02049</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Dominique</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brooks</t>
+          <t>Bailey</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1589,7 +1577,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1598,48 +1586,50 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>matthew_brooks@gmail.com</t>
+          <t>dominique.bailey325@outlook.com</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0957121403</t>
+          <t>260950050331</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>05/06/2020</t>
+          <t>2020/04/13</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Mansa</t>
+          <t>LUSAKA</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Joseph Brooks</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>Kristen Bailey</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>94.59999999999999</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STU02917</t>
+          <t>STU00865</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Marks</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1648,125 +1638,125 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>josephw7@yahoo.com</t>
+          <t>nancy.marks741@gmail.com</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(97) 1508563</t>
+          <t>260956727792</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>02/04/2021</t>
+          <t>2019/06/05</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2.72</v>
+        <v>3.78</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>chipata</t>
+          <t>solwezi</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Kayla Wilson</t>
+          <t>Joshua Marks</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>69.5</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STU00503</t>
+          <t>STU02475</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alicia   </t>
+          <t xml:space="preserve">Wendy   </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Randall</t>
+          <t>Cole</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>aliciar18@gmail.com</t>
+          <t>wendy_cole@school.edu.zm</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>260973983507</t>
+          <t>+260-97-8903263</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>08 Apr 2018</t>
+          <t>2020-07-20</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>3.18</v>
+        <v>3.76</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Chingola</t>
+          <t>NDOLA</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Tracy Randall</t>
+          <t>Samuel  Cole</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>76</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STU00865</t>
+          <t>STU04556</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Douglas</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Marks</t>
+          <t xml:space="preserve">Martinez   </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1774,55 +1764,51 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>nancy.marks741@gmail.com</t>
+          <t>douglasm94@yahoo.com</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>260956727792</t>
+          <t>0952684383</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2019/06/05</t>
+          <t>22/12/2019</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>solwezi</t>
-        </is>
-      </c>
+        <v>3.44</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Joshua Marks</t>
+          <t>Anita Martinez</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>70.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STU02009</t>
+          <t>STU03820</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Guerra</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1831,177 +1817,179 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>michael_guerra@school.edu.zm</t>
+          <t>jason.may184@school.edu.zm</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0955328499</t>
+          <t>(96) 8241125</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>06-15-2019</t>
+          <t>02-15-2024</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Mansa</t>
+          <t xml:space="preserve">Lusaka   </t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Alexa  Guerra</t>
+          <t>Tara  May</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>68.7</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STU00282</t>
+          <t>STU02779</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Wendy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>Dixon</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>amanda.stone152@yahoo.com</t>
+          <t>wendy.dixon771@outlook.com</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(96) 8304611</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>0962069387</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2024-01-14</t>
+        </is>
+      </c>
       <c r="J25" t="n">
-        <v>3.73</v>
+        <v>3.37</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Livingstone</t>
+          <t>MONGU</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Nicholas Stone</t>
+          <t>Jeremy  Dixon</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>87.5</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STU03341</t>
+          <t>STU03756</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Roberts</t>
+          <t>Brooks</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>michelle.roberts370@gmail.com</t>
+          <t>matthew_brooks@gmail.com</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>+260-95-4739571</t>
+          <t>0957121403</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2018/03/19</t>
+          <t>05/06/2020</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>1.46</v>
+        <v>2.2</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Chipata</t>
+          <t>Mansa</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Bryan Roberts</t>
-        </is>
-      </c>
-      <c r="M26" t="n">
-        <v>89</v>
-      </c>
+          <t>Joseph Brooks</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STU02475</t>
+          <t>STU03638</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wendy   </t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cole</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2010,59 +1998,59 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>wendy_cole@school.edu.zm</t>
+          <t>julie.taylor60@yahoo.com</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>+260-97-8903263</t>
+          <t>(97) 4563439</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2020-07-20</t>
+          <t>17/08/2021</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>3.76</v>
+        <v>1.77</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>NDOLA</t>
+          <t>Lusaka</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Samuel  Cole</t>
+          <t>Laura  Taylor</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>65.40000000000001</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STU02854</t>
+          <t>STU02819</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Martinez</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2071,120 +2059,120 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>xavier_martinez@gmail.com</t>
+          <t>linda.johnson214@yahoo.com</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(97) 4931437</t>
+          <t>0961479005</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2022/08/27</t>
+          <t>2020-03-23</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>3.16</v>
+        <v>3.33</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>mansa</t>
+          <t>Lusaka</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Bobby  Martinez</t>
+          <t>Kathryn Johnson</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>96.5</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STU00679</t>
+          <t>STU00732</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Susan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tyler</t>
+          <t>Bird</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>joseph.tyler946@school.edu.zm</t>
+          <t>susan_bird@gmail.com</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>260963477249</t>
+          <t>(97) 2742095</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>08 Jan 2023</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>2.62</v>
+        <v>2.19</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">kitwe   </t>
+          <t>Mongu</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Alexandra  Tyler</t>
+          <t xml:space="preserve">  Justin Bird</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>63.1</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STU02955</t>
+          <t>STU00145</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeffrey   </t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Obrien</t>
+          <t>Shelton</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2193,482 +2181,474 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>jeffrey.obrien701@outlook.com</t>
+          <t>amanda_shelton@yahoo.com</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0974117026</t>
+          <t>(95) 6960666</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>06/03/2019</t>
+          <t>07-03-2020</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>1.05</v>
+        <v>3.66</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Chipata</t>
+          <t>Kabwe</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melissa Obrien   </t>
+          <t>Gabriella  Shelton</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>96.7</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STU04902</t>
+          <t>STU01060</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Amy</t>
+          <t>Adrienne</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flores   </t>
+          <t>Bauer</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>amy.flores853@school.edu.zm</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(96) 5973257</t>
-        </is>
-      </c>
+          <t>adrienneb90@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2018/11/29</t>
+          <t>02 Sep 2022</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>2.54</v>
+        <v>3.94</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Livingstone</t>
+          <t>Chingola</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Edward  Flores</t>
+          <t xml:space="preserve">  Steven Bauer</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>97.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STU02875</t>
+          <t>STU02335</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tamara</t>
+          <t>Zachary</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anderson   </t>
+          <t>Cook</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>tamaraa62@gmail.com</t>
+          <t>zachary_cook@outlook.com</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0952941834</t>
+          <t>(97) 5757898</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2019-12-21</t>
+          <t>05 Mar 2021</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>chipata</t>
-        </is>
-      </c>
+        <v>2.33</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Brandon  Anderson</t>
+          <t>Heidi Cook</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>72.3</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STU00915</t>
+          <t>STU04436</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joseph   </t>
+          <t xml:space="preserve">Elizabeth   </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Roberts</t>
+          <t>Herrera</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grade 8</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>joseph.roberts878@gmail.com</t>
-        </is>
-      </c>
+          <t>Grade 4</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(95) 7735594</t>
+          <t>0956676160</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>23/04/2018</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>1.62</v>
+        <v>2.26</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>ndola</t>
+          <t>NDOLA</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Jacob Roberts</t>
+          <t xml:space="preserve">  Austin Herrera</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>87</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STU01942</t>
+          <t>STU02632</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t xml:space="preserve">Mark   </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chambers</t>
+          <t>Berry</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>kathyc2@yahoo.com</t>
+          <t>markb13@yahoo.com</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0957699314</t>
+          <t>0958362080</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>07/05/2021</t>
+          <t>31/07/2024</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>1.15</v>
+        <v>4</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Mansa</t>
+          <t>ndola</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Jacob Chambers</t>
+          <t>Christian Berry</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>79.8</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STU00277</t>
+          <t>STU01292</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Megan</t>
+          <t>Jeffrey</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Adams</t>
+          <t xml:space="preserve">Romero   </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>12</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Grade 4</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>megan.adams182@school.edu.zm</t>
+          <t>jeffrey.romero723@outlook.com</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>260960168488</t>
+          <t>260976857486</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>04 Nov 2019</t>
+          <t>10-01-2020</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>1.94</v>
+        <v>3.32</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Solwezi</t>
+          <t>CHIPATA</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Kelly Adams</t>
+          <t>Sheryl  Romero</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>82.2</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STU02825</t>
+          <t>STU00066</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Catherine</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gutierrez</t>
+          <t>Lara</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>jason.gutierrez701@outlook.com</t>
+          <t>catherine.lara811@school.edu.zm</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>+260-97-6862340</t>
+          <t>+260-97-7815076</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>03-22-2024</t>
+          <t>2022/01/28</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>2.82</v>
+        <v>3.04</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>lusaka</t>
+          <t>NDOLA</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Grace Gutierrez</t>
+          <t>Jose Lara</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>95.09999999999999</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STU00630</t>
+          <t>STU02745</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Becker</t>
+          <t xml:space="preserve">Wise   </t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>josephb48@gmail.com</t>
+          <t>thomas_wise@gmail.com</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>260960639000</t>
+          <t>260970116159</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10-04-2020</t>
+          <t>2023/07/01</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ndola</t>
+          <t xml:space="preserve">Ndola   </t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>David Becker</t>
+          <t>Michelle Wise</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>65.5</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STU02853</t>
+          <t>STU02009</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dawn</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parker   </t>
+          <t>Guerra</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2677,59 +2657,59 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>dawnp40@school.edu.zm</t>
+          <t>michael_guerra@school.edu.zm</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0978948248</t>
+          <t>0955328499</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2018-09-06</t>
+          <t>06-15-2019</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>3.15</v>
+        <v>3.26</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHINGOLA   </t>
+          <t>Mansa</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Richard Parker</t>
+          <t>Alexa  Guerra</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>79.7</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STU02155</t>
+          <t>STU03854</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Glenn</t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Wright</t>
+          <t>Rivera</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2738,55 +2718,55 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>+260-95-2313269</t>
+          <t>(97) 5552152</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>18/11/2019</t>
+          <t>2021/12/20</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>1.74</v>
+        <v>1.34</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Chipata</t>
+          <t xml:space="preserve">  Lusaka</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>John Wright</t>
+          <t xml:space="preserve">  Justin Rivera</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>91.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STU00854</t>
+          <t>STU02875</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nicholas   </t>
+          <t>Tamara</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Matthews</t>
+          <t xml:space="preserve">Anderson   </t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2795,59 +2775,59 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>nicholas.matthews24@yahoo.com</t>
+          <t>tamaraa62@gmail.com</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>+260-97-6924408</t>
+          <t>0952941834</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2021-07-17</t>
+          <t>2019-12-21</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>1.39</v>
+        <v>7.56</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>solwezi</t>
+          <t>chipata</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Jason Matthews</t>
+          <t>Brandon  Anderson</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>82.3</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STU01417</t>
+          <t>STU02007</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t xml:space="preserve">Joshua   </t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Gentry</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2856,60 +2836,60 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(95) 1192682</t>
+          <t>0954277885</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2021/08/25</t>
+          <t>2018/09/24</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>2.83</v>
+        <v>1.32</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Chingola</t>
+          <t>Solwezi</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Jonathan Gentry</t>
+          <t xml:space="preserve">Kimberly Smith   </t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>96</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STU02219</t>
+          <t>STU00503</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ebony   </t>
+          <t xml:space="preserve">Alicia   </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Randall</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -2917,39 +2897,39 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ebony.thompson204@outlook.com</t>
+          <t>aliciar18@gmail.com</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>260954933990</t>
+          <t>260973983507</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10-10-2022</t>
+          <t>08 Apr 2018</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>3.95</v>
+        <v>3.18</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Chipata</t>
+          <t>Chingola</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Michael Thompson</t>
+          <t>Tracy Randall</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43">
@@ -2978,7 +2958,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3016,17 +2996,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STU03638</t>
+          <t>STU02219</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t xml:space="preserve">Ebony   </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Thompson</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3035,148 +3015,152 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>julie.taylor60@yahoo.com</t>
+          <t>ebony.thompson204@outlook.com</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(97) 4563439</t>
+          <t>260954933990</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>17/08/2021</t>
+          <t>10-10-2022</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>1.77</v>
+        <v>3.95</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Lusaka</t>
+          <t>Chipata</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Laura  Taylor</t>
+          <t>Michael Thompson</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>81.8</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STU01837</t>
+          <t>STU00277</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Paige</t>
+          <t>Megan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Harper</t>
+          <t>Adams</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>paigeh91@school.edu.zm</t>
+          <t>megan.adams182@school.edu.zm</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>260963796316</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>260960168488</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>04 Nov 2019</t>
+        </is>
+      </c>
       <c r="J45" t="n">
-        <v>3.39</v>
+        <v>1.94</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Chipata</t>
+          <t>Solwezi</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Shannon Harper</t>
+          <t>Kelly Adams</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>97.5</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STU04241</t>
+          <t>STU03253</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grace   </t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valentine   </t>
+          <t xml:space="preserve">Williams   </t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>grace_valentine@gmail.com</t>
+          <t>erinw52@school.edu.zm</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(95) 1764359</t>
+          <t>260959255370</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2019/01/12</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>1.27</v>
+        <v>3.05</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -3185,88 +3169,88 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Michael  Valentine</t>
+          <t xml:space="preserve">Brian Williams   </t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>75.90000000000001</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STU01881</t>
+          <t>STU01280</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Adrian</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>Khan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>jacqueline.thompson387@yahoo.com</t>
+          <t>adrian.khan609@gmail.com</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>+260-97-1667503</t>
+          <t>0977658917</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>30 May 2022</t>
+          <t>2022/06/15</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>1.92</v>
+        <v>3.15</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Chingola</t>
+          <t>LIVINGSTONE</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeffrey Short   </t>
+          <t xml:space="preserve">  Christopher Khan</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>78.90000000000001</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STU02049</t>
+          <t>STU02155</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dominique</t>
+          <t>Glenn</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bailey</t>
+          <t>Wright</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3275,59 +3259,55 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grade 3</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>dominique.bailey325@outlook.com</t>
-        </is>
-      </c>
+          <t>Grade 7</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>260950050331</t>
+          <t>+260-95-2313269</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2020/04/13</t>
+          <t>18/11/2019</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>LUSAKA</t>
+          <t>Chipata</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Kristen Bailey</t>
+          <t>John Wright</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>94.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STU01421</t>
+          <t>STU00389</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Crystal</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Welch</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3336,55 +3316,59 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>14</v>
-      </c>
-      <c r="F49" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Grade 7</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>crystal_welch@yahoo.com</t>
+          <t>eric.parker190@school.edu.zm</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0965352275</t>
+          <t>+260-97-9229532</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2018-04-18</t>
+          <t>01-09-2020</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>3.78</v>
+        <v>1.49</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>lusaka</t>
+          <t>Kitwe</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Steven  Welch</t>
+          <t>Mark Parker</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>74.90000000000001</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STU01999</t>
+          <t>STU00528</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Darrell</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Peterson</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3393,120 +3377,116 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>darrells59@gmail.com</t>
+          <t>josephp43@gmail.com</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>+260-96-6530043</t>
+          <t>260960302230</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2022-02-03</t>
+          <t>28 Jan 2023</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solwezi   </t>
+          <t>CHIPATA</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Kristen Smith</t>
+          <t xml:space="preserve">Jason Peterson   </t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>78.3</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STU02779</t>
+          <t>STU01417</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wendy</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dixon</t>
+          <t>Gentry</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grade 8</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>wendy.dixon771@outlook.com</t>
-        </is>
-      </c>
+          <t>Grade 7</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0962069387</t>
+          <t>(95) 1192682</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2021/08/25</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>3.37</v>
+        <v>2.83</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>MONGU</t>
+          <t>Chingola</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Jeremy  Dixon</t>
+          <t>Jonathan Gentry</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>62.6</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STU01060</t>
+          <t>STU00854</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Adrienne</t>
+          <t xml:space="preserve">Nicholas   </t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bauer</t>
+          <t>Matthews</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3515,171 +3495,181 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>adrienneb90@yahoo.com</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>nicholas.matthews24@yahoo.com</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+260-97-6924408</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>02 Sep 2022</t>
+          <t>2021-07-17</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>3.94</v>
+        <v>1.39</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Chingola</t>
+          <t>solwezi</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Steven Bauer</t>
+          <t>Jason Matthews</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>78.40000000000001</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STU02007</t>
+          <t>STU03665</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joshua   </t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Ramos</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grade 8</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>Grade 7</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>maria_ramos@school.edu.zm</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0954277885</t>
+          <t>0953022756</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2018/09/24</t>
+          <t>11-12-2022</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Solwezi</t>
+          <t>CHINGOLA</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kimberly Smith   </t>
+          <t xml:space="preserve">Kimberly Ramos   </t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>89.7</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STU00432</t>
+          <t>STU01421</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t xml:space="preserve">  Crystal</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Huang</t>
+          <t xml:space="preserve">  Welch</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>charles.huang142@gmail.com</t>
+          <t>crystal_welch@yahoo.com</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>+260-97-3601089</t>
+          <t>0965352275</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>12-19-2018</t>
+          <t>2018-04-18</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>3.2</v>
+        <v>3.78</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>solwezi</t>
+          <t>lusaka</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Troy Huang</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr"/>
+          <t>Steven  Welch</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>74.90000000000001</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STU00732</t>
+          <t>STU04241</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Susan</t>
+          <t xml:space="preserve">Grace   </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bird</t>
+          <t xml:space="preserve">Valentine   </t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3688,59 +3678,59 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>susan_bird@gmail.com</t>
+          <t>grace_valentine@gmail.com</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(97) 2742095</t>
+          <t>(95) 1764359</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2019/01/12</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>2.19</v>
+        <v>1.27</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Mongu</t>
+          <t>mansa</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Justin Bird</t>
+          <t>Michael  Valentine</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>99.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STU04540</t>
+          <t>STU00970</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Stephens</t>
+          <t>Rogers</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3749,59 +3739,59 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>victoria_stephens@outlook.com</t>
+          <t>scott_rogers@gmail.com</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>+260-96-9753702</t>
+          <t>0956918034</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2019/04/04</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Mongu</t>
+          <t>Chipata</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Brian Stephens</t>
+          <t xml:space="preserve">Samantha Rogers   </t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>85.5</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STU01907</t>
+          <t>STU01942</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Chambers</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3810,91 +3800,91 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>john.johnson635@outlook.com</t>
+          <t>kathyc2@yahoo.com</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0977152757</t>
+          <t>0957699314</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>04-09-2022</t>
+          <t>07/05/2021</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>2.91</v>
+        <v>1.15</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>SOLWEZI</t>
+          <t>Mansa</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Brad Johnson</t>
+          <t>Jacob Chambers</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>94.59999999999999</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STU00735</t>
+          <t>STU00172</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Donna</t>
+          <t>Brent</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Whitehead</t>
+          <t>Ramos</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>donna_whitehead@gmail.com</t>
+          <t>brent.ramos229@yahoo.com</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0963635975</t>
+          <t>0963246154</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>09/05/2024</t>
+          <t>2023/03/19</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -3903,27 +3893,27 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Angela Whitehead</t>
+          <t>Anna Ramos</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>65.8</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STU04454</t>
+          <t>STU04800</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Robin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Watson   </t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3932,7 +3922,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3941,50 +3931,50 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>robin_watson@gmail.com</t>
+          <t>jeremy.jones934@school.edu.zm</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>260962432072</t>
+          <t>(95) 4386945</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2022/04/30</t>
+          <t>01-14-2021</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>1.44</v>
+        <v>2.96</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Kabwe</t>
+          <t>Kitwe</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Anthony Watson</t>
+          <t>Bryan Jones</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>91.59999999999999</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STU00260</t>
+          <t>STU02686</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Rebecca</t>
+          <t xml:space="preserve">  Crystal</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Randall</t>
+          <t>Cooper</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3993,59 +3983,55 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grade 11</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>rebecca.randall682@outlook.com</t>
-        </is>
-      </c>
+          <t>Grade 9</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>260964940322</t>
+          <t>+260-95-8899713</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>02-19-2023</t>
+          <t>05/09/2023</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>3.69</v>
+        <v>2.95</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>CHINGOLA</t>
+          <t xml:space="preserve">  KITWE</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Kevin Randall</t>
+          <t xml:space="preserve">Malik Cooper   </t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>71.5</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STU02797</t>
+          <t>STU02853</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Dawn</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Harper</t>
+          <t xml:space="preserve">Parker   </t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4054,238 +4040,240 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>150</v>
-      </c>
-      <c r="F61" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Grade 9</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>danielh81@school.edu.zm</t>
+          <t>dawnp40@school.edu.zm</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>260962229135</t>
+          <t>0978948248</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>06/01/2018</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>3.51</v>
+        <v>3.15</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Kitwe</t>
+          <t xml:space="preserve">CHINGOLA   </t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Dustin Harper</t>
+          <t>Richard Parker</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>73.40000000000001</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STU04212</t>
+          <t>STU03931</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Heather</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Gomez</t>
+          <t>Hayes</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>heather.gomez239@yahoo.com</t>
+          <t>roberth51@school.edu.zm</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>260950872054</t>
+          <t>0967555523</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2018/11/10</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>3.17</v>
-      </c>
+          <t>16 Sep 2024</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>mansa</t>
+          <t>chingola</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Travis Gomez</t>
+          <t>Jessica Hayes</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>94.40000000000001</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STU04520</t>
+          <t>STU01296</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Catherine</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Curtis   </t>
+          <t>Reid</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>catherine.curtis822@yahoo.com</t>
+          <t>richardr35@gmail.com</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(96) 3170103</t>
+          <t>0953489781</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>22 Feb 2023</t>
+          <t>26 Jan 2024</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>2.05</v>
+        <v>3.16</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Mongu</t>
+          <t>LIVINGSTONE</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Robert Curtis</t>
+          <t>Mikayla Reid</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>85.3</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STU03699</t>
+          <t>STU04902</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t xml:space="preserve">  Amy</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fletcher   </t>
+          <t xml:space="preserve">Flores   </t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>scott.fletcher629@gmail.com</t>
+          <t>amy.flores853@school.edu.zm</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>+260-95-4915203</t>
+          <t>(96) 5973257</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>09/05/2022</t>
+          <t>2018/11/29</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SOLWEZI</t>
+          <t>Livingstone</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Melissa  Fletcher</t>
+          <t>Edward  Flores</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>85</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STU03356</t>
+          <t>STU02955</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Christopher</t>
+          <t xml:space="preserve">Jeffrey   </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Webb</t>
+          <t>Obrien</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4294,57 +4282,59 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>christopher.webb735@outlook.com</t>
+          <t>jeffrey.obrien701@outlook.com</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0975718099</t>
+          <t>0974117026</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>27/01/2020</t>
+          <t>06/03/2019</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>3.25</v>
+        <v>1.05</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>chingola</t>
+          <t>Chipata</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Alexis Webb</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr"/>
+          <t xml:space="preserve">Melissa Obrien   </t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>96.7</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STU02367</t>
+          <t>STU02596</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>William</t>
+          <t xml:space="preserve">  David</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Zuniga</t>
+          <t>Jacobson</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4353,181 +4343,175 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>williamz39@gmail.com</t>
+          <t>david_jacobson@school.edu.zm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(96) 9367470</t>
+          <t>+260-95-8348268</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2023/01/15</t>
+          <t>03 Apr 2023</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>1.53</v>
+        <v>3.99</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Ndola</t>
+          <t>MONGU</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Ann Zuniga</t>
-        </is>
-      </c>
-      <c r="M66" t="n">
-        <v>68.5</v>
-      </c>
+          <t>Zachary Jacobson</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STU00970</t>
+          <t>STU03913</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t xml:space="preserve">  Kevin</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rogers</t>
+          <t>Lane</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>scott_rogers@gmail.com</t>
+          <t>kevinl33@outlook.com</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0956918034</t>
+          <t>+260-96-2128812</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>23 Nov 2019</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>2.81</v>
+        <v>2.26</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Chipata</t>
+          <t>Ndola</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samantha Rogers   </t>
+          <t xml:space="preserve">Emily Lane   </t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>85.09999999999999</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STU00528</t>
+          <t>STU02190</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Peterson</t>
-        </is>
-      </c>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>josephp43@gmail.com</t>
+          <t>richardr56@gmail.com</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>260960302230</t>
+          <t>+260-97-4851171</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>28 Jan 2023</t>
+          <t>12 Jun 2021</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>3.82</v>
+        <v>2.33</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>CHIPATA</t>
+          <t xml:space="preserve">Ndola   </t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jason Peterson   </t>
+          <t xml:space="preserve">  Misty Roberts</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>67.8</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STU03931</t>
+          <t>STU01881</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>John</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hayes</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4536,57 +4520,59 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>roberth51@school.edu.zm</t>
+          <t>jacqueline.thompson387@yahoo.com</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0967555523</t>
+          <t>+260-97-1667503</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>16 Sep 2024</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr"/>
+          <t>30 May 2022</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>1.92</v>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>chingola</t>
+          <t xml:space="preserve">  Chingola</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Jessica Hayes</t>
+          <t xml:space="preserve">Jeffrey Short   </t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>89.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STU04713</t>
+          <t>STU00260</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kathryn</t>
+          <t>Rebecca</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Shields</t>
+          <t>Randall</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4595,59 +4581,59 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>kathryns57@school.edu.zm</t>
+          <t>rebecca.randall682@outlook.com</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>+260-97-2662290</t>
+          <t>260964940322</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>04/09/2020</t>
+          <t>02-19-2023</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>2.83</v>
+        <v>3.69</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Ndola</t>
+          <t>CHINGOLA</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Wesley  Shields</t>
+          <t>Kevin Randall</t>
         </is>
       </c>
       <c r="M70" t="n">
-        <v>60.9</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STU00066</t>
+          <t>STU00630</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Catherine</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lara</t>
+          <t>Becker</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4656,120 +4642,120 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>catherine.lara811@school.edu.zm</t>
+          <t>josephb48@gmail.com</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>+260-97-7815076</t>
+          <t>260960639000</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2022/01/28</t>
+          <t>10-04-2020</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>3.04</v>
+        <v>2.28</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>NDOLA</t>
+          <t xml:space="preserve">  ndola</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Jose Lara</t>
+          <t>David Becker</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>65</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STU00206</t>
+          <t>STU01999</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Darrell</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ronald_turner@outlook.com</t>
+          <t>darrells59@gmail.com</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>260954044668</t>
+          <t>+260-96-6530043</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2020/07/17</t>
+          <t>2022-02-03</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>2.9</v>
+        <v>3.81</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>solwezi</t>
+          <t xml:space="preserve">Solwezi   </t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Michael Turner</t>
+          <t>Kristen Smith</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>66</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STU01895</t>
+          <t>STU01907</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steven   </t>
+          <t>John</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4778,59 +4764,59 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stevenw52@school.edu.zm</t>
+          <t>john.johnson635@outlook.com</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>260957565368</t>
+          <t>0977152757</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>06-15-2020</t>
+          <t>04-09-2022</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>2.07</v>
+        <v>2.91</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Livingstone</t>
+          <t>SOLWEZI</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Sean Williams</t>
+          <t>Brad Johnson</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>82.3</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STU01078</t>
+          <t>STU03341</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tyrone</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dennis</t>
+          <t xml:space="preserve">  Roberts</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4839,112 +4825,120 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>tyrone.dennis470@outlook.com</t>
+          <t>michelle.roberts370@gmail.com</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>0979016612</t>
+          <t>+260-95-4739571</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2021-03-19</t>
+          <t>2018/03/19</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chingola   </t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
+          <t>Chipata</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Bryan Roberts</t>
+        </is>
+      </c>
       <c r="M74" t="n">
-        <v>95.40000000000001</v>
+        <v>89</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STU04436</t>
+          <t>STU00915</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elizabeth   </t>
+          <t xml:space="preserve">Joseph   </t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Herrera</t>
+          <t>Roberts</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grade 8</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
+          <t>Grade 11</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>joseph.roberts878@gmail.com</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>0956676160</t>
+          <t>(95) 7735594</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>23/04/2018</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>2.26</v>
+        <v>1.62</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>NDOLA</t>
+          <t>ndola</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Austin Herrera</t>
+          <t>Jacob Roberts</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>93.59999999999999</v>
+        <v>87</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STU02819</t>
+          <t>STU04454</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t xml:space="preserve">Watson   </t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4953,59 +4947,59 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>linda.johnson214@yahoo.com</t>
+          <t>robin_watson@gmail.com</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>0961479005</t>
+          <t>260962432072</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2020-03-23</t>
+          <t>2022/04/30</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>3.33</v>
+        <v>1.44</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Lusaka</t>
+          <t>Kabwe</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Kathryn Johnson</t>
+          <t xml:space="preserve">  Anthony Watson</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>63.2</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STU01110</t>
+          <t>STU01032</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Jeffrey</t>
+          <t>Loretta</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Davis</t>
+          <t>Foster</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5014,177 +5008,181 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>-5</v>
+        <v>18</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>jeffrey.davis931@yahoo.com</t>
+          <t>loretta_foster@gmail.com</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>+260-96-9072838</t>
+          <t>260974160580</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2020/09/18</t>
+          <t>10-23-2023</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="K77" t="inlineStr"/>
+        <v>1.81</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Solwezi</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Morgan Davis</t>
+          <t xml:space="preserve">Juan Foster   </t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>63.5</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STU00389</t>
+          <t>STU00654</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t xml:space="preserve">  Sara</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Barnes</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>eric.parker190@school.edu.zm</t>
+          <t>sara.barnes700@outlook.com</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>+260-97-9229532</t>
+          <t>+260-97-1390306</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>01-09-2020</t>
+          <t>13 Dec 2018</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>1.49</v>
+        <v>2.23</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Kitwe</t>
+          <t>Chingola</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Mark Parker</t>
+          <t xml:space="preserve">William Barnes   </t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>77.09999999999999</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STU04665</t>
+          <t>STU02854</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Zoe</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>Martinez</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>zoet9@gmail.com</t>
+          <t>xavier_martinez@gmail.com</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>260964790292</t>
+          <t>(97) 4931437</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>12 Feb 2018</t>
+          <t>2022/08/27</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>2.39</v>
+        <v>3.16</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Chipata</t>
+          <t>mansa</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Ryan Turner</t>
+          <t>Bobby  Martinez</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>66.40000000000001</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STU04009</t>
+          <t>STU00679</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Kathleen</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cole</t>
+          <t>Tyler</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5193,59 +5191,59 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>kathleen.cole957@outlook.com</t>
+          <t>joseph.tyler946@school.edu.zm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0957848571</t>
+          <t>260963477249</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2023/08/23</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>1.69</v>
+        <v>2.62</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Chingola</t>
+          <t xml:space="preserve">kitwe   </t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Isaac Cole</t>
+          <t>Alexandra  Tyler</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>84.7</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STU04800</t>
+          <t>STU03001</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t xml:space="preserve">Rodriguez   </t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5254,116 +5252,116 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>jeremy.jones934@school.edu.zm</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(95) 4386945</t>
-        </is>
-      </c>
+          <t>ericr91@gmail.com</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>01-14-2021</t>
+          <t>03/01/2022</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>2.96</v>
+        <v>2.63</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Kitwe</t>
+          <t xml:space="preserve">  Chingola</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Bryan Jones</t>
+          <t xml:space="preserve">  David Rodriguez</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>89.5</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STU03854</t>
+          <t>STU00206</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rivera</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grade 5</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>ronald_turner@outlook.com</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(97) 5552152</t>
+          <t>260954044668</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2021/12/20</t>
+          <t>2020/07/17</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>1.34</v>
+        <v>2.9</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Lusaka</t>
+          <t>solwezi</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Justin Rivera</t>
+          <t xml:space="preserve">  Michael Turner</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>80.59999999999999</v>
+        <v>66</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STU03001</t>
+          <t>STU04540</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rodriguez   </t>
+          <t>Stephens</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5376,108 +5374,116 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>ericr91@gmail.com</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>victoria_stephens@outlook.com</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>+260-96-9753702</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>03/01/2022</t>
+          <t>2019/04/04</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Chingola</t>
+          <t>Mongu</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">  David Rodriguez</t>
+          <t>Brian Stephens</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>66.7</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STU02190</t>
+          <t>STU03457</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Richard</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>Rebekah</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>richardr56@gmail.com</t>
+          <t>rebekah.brown888@outlook.com</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>+260-97-4851171</t>
+          <t>(97) 7134382</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>12 Jun 2021</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>2.33</v>
+        <v>3.72</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ndola   </t>
+          <t>chingola</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Misty Roberts</t>
+          <t>Kayla Brown</t>
         </is>
       </c>
       <c r="M84" t="n">
-        <v>89.7</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STU00561</t>
+          <t>STU01919</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Marilyn</t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Becker   </t>
+          <t xml:space="preserve">  Grimes</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5485,276 +5491,101 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="E85" t="n">
-        <v>6</v>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>marilyn_becker@outlook.com</t>
+          <t>amanda.grimes785@outlook.com</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>+260-95-9250481</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(95) 8857227</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>08-31-2019</t>
+        </is>
+      </c>
       <c r="J85" t="n">
-        <v>3.96</v>
+        <v>3.21</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>kabwe</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
+          <t>Mongu</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Mary Grimes</t>
+        </is>
+      </c>
       <c r="M85" t="n">
-        <v>96.7</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STU02632</t>
+          <t>STU01514</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mark   </t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Berry</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>10</v>
-      </c>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>markb13@yahoo.com</t>
+          <t>henry_lee@gmail.com</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>0958362080</t>
+          <t>0978851786</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>31/07/2024</t>
+          <t>2022-05-28</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>4</v>
+        <v>1.98</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>ndola</t>
+          <t xml:space="preserve">  LUSAKA</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Christian Berry</t>
+          <t xml:space="preserve">  Denise Lee</t>
         </is>
       </c>
       <c r="M86" t="n">
-        <v>65.09999999999999</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>STU01292</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Jeffrey</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Romero   </t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>10</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Grade 2</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>jeffrey.romero723@outlook.com</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>260976857486</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>10-01-2020</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>CHIPATA</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>Sheryl  Romero</t>
-        </is>
-      </c>
-      <c r="M87" t="n">
-        <v>92.40000000000001</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>STU02335</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Zachary</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Cook</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>10</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Grade 11</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>zachary_cook@outlook.com</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(97) 5757898</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>05 Mar 2021</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>Heidi Cook</t>
-        </is>
-      </c>
-      <c r="M88" t="n">
-        <v>89.2</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>STU01296</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Richard</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Reid</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>15</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Grade 10</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>richardr35@gmail.com</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>0953489781</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>26 Jan 2024</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>LIVINGSTONE</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>Mikayla Reid</t>
-        </is>
-      </c>
-      <c r="M89" t="n">
-        <v>62.5</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Pandas/Datasets/students_clean.xlsx
+++ b/Pandas/Datasets/students_clean.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,12 +26,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -545,59 +559,59 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>STU01110</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Jeffrey</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">  Davis</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Grade 1</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>jeffrey.davis931@yahoo.com</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>+260-96-9072838</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>2020/09/18</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="1" t="n">
         <v>1.52</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr"/>
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>Morgan Davis</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="1" t="n">
         <v>63.5</v>
       </c>
     </row>
@@ -842,63 +856,63 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>STU02843</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>Christopher</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>Brown</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>Grade 1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>christopher_brown@gmail.com</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>0962209692</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="1" t="inlineStr">
         <is>
           <t>27 Mar 2023</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="1" t="n">
         <v>1.3</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="1" t="inlineStr">
         <is>
           <t>CHIPATA</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="1" t="inlineStr">
         <is>
           <t>Vanessa Brown</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="1" t="n">
         <v>70.3</v>
       </c>
     </row>
@@ -1017,59 +1031,59 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>STU01078</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>Tyrone</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>Dennis</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>Grade 1</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>tyrone.dennis470@outlook.com</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>0979016612</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>2021-03-19</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="1" t="n">
         <v>1.42</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Chingola   </t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
+      <c r="L11" s="1" t="inlineStr"/>
+      <c r="M11" s="1" t="n">
         <v>95.40000000000001</v>
       </c>
     </row>
@@ -1135,63 +1149,63 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>STU03356</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Christopher</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Webb</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Grade 1</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>christopher.webb735@outlook.com</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>0975718099</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>27/01/2020</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="2" t="n">
         <v>3.25</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>chingola</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>Alexis Webb</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1377,124 +1391,124 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>STU02367</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>William</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>Zuniga</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="1" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="1" t="inlineStr">
         <is>
           <t>Grade 2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>williamz39@gmail.com</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="1" t="inlineStr">
         <is>
           <t>(96) 9367470</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="1" t="inlineStr">
         <is>
           <t>2023/01/15</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="1" t="n">
         <v>1.53</v>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="1" t="inlineStr">
         <is>
           <t>Ndola</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" s="1" t="inlineStr">
         <is>
           <t>Ann Zuniga</t>
         </is>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="1" t="n">
         <v>68.5</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>STU04009</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>Kathleen</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>Cole</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="1" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>Grade 2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>kathleen.cole957@outlook.com</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="1" t="inlineStr">
         <is>
           <t>0957848571</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="1" t="inlineStr">
         <is>
           <t>2023/08/23</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="1" t="n">
         <v>1.69</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="1" t="inlineStr">
         <is>
           <t>Chingola</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">  Isaac Cole</t>
         </is>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" s="1" t="n">
         <v>84.7</v>
       </c>
     </row>
@@ -1556,63 +1570,63 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>STU02049</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>Dominique</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>Bailey</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="1" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="1" t="inlineStr">
         <is>
           <t>Grade 2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>dominique.bailey325@outlook.com</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="1" t="inlineStr">
         <is>
           <t>260950050331</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="1" t="inlineStr">
         <is>
           <t>2020/04/13</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="1" t="n">
         <v>1.83</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="1" t="inlineStr">
         <is>
           <t>LUSAKA</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" s="1" t="inlineStr">
         <is>
           <t>Kristen Bailey</t>
         </is>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="1" t="n">
         <v>94.59999999999999</v>
       </c>
     </row>
@@ -1918,122 +1932,122 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>STU03756</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Matthew</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Brooks</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Grade 3</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>matthew_brooks@gmail.com</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>0957121403</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>05/06/2020</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>Mansa</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>Joseph Brooks</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>STU03638</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t>Julie</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>Taylor</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="1" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="1" t="inlineStr">
         <is>
           <t>Grade 3</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
         <is>
           <t>julie.taylor60@yahoo.com</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="1" t="inlineStr">
         <is>
           <t>(97) 4563439</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="1" t="inlineStr">
         <is>
           <t>17/08/2021</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" s="1" t="n">
         <v>1.77</v>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" s="1" t="inlineStr">
         <is>
           <t>Lusaka</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L27" s="1" t="inlineStr">
         <is>
           <t>Laura  Taylor</t>
         </is>
       </c>
-      <c r="M27" t="n">
+      <c r="M27" s="1" t="n">
         <v>81.8</v>
       </c>
     </row>
@@ -2697,59 +2711,59 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>STU03854</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="1" t="inlineStr">
         <is>
           <t>Amanda</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>Rivera</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="1" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="1" t="inlineStr">
         <is>
           <t>Grade 6</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
+      <c r="G39" s="1" t="inlineStr"/>
+      <c r="H39" s="1" t="inlineStr">
         <is>
           <t>(97) 5552152</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" s="1" t="inlineStr">
         <is>
           <t>2021/12/20</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" s="1" t="n">
         <v>1.34</v>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K39" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">  Lusaka</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L39" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">  Justin Rivera</t>
         </is>
       </c>
-      <c r="M39" t="n">
+      <c r="M39" s="1" t="n">
         <v>80.59999999999999</v>
       </c>
     </row>
@@ -2815,59 +2829,59 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>STU02007</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Joshua   </t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>Smith</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="1" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="1" t="inlineStr">
         <is>
           <t>Grade 6</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
+      <c r="G41" s="1" t="inlineStr"/>
+      <c r="H41" s="1" t="inlineStr">
         <is>
           <t>0954277885</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" s="1" t="inlineStr">
         <is>
           <t>2018/09/24</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="J41" s="1" t="n">
         <v>1.32</v>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K41" s="1" t="inlineStr">
         <is>
           <t>Solwezi</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L41" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Kimberly Smith   </t>
         </is>
       </c>
-      <c r="M41" t="n">
+      <c r="M41" s="1" t="n">
         <v>89.7</v>
       </c>
     </row>
@@ -2933,63 +2947,63 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="1" t="inlineStr">
         <is>
           <t>STU03844</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="1" t="inlineStr">
         <is>
           <t>Eric</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">  Richardson</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="1" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="1" t="inlineStr">
         <is>
           <t>Grade 6</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="1" t="inlineStr">
         <is>
           <t>eric.richardson577@outlook.com</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="1" t="inlineStr">
         <is>
           <t>+260-95-8992886</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" s="1" t="inlineStr">
         <is>
           <t>08-16-2021</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" s="1" t="n">
         <v>1.65</v>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Ndola   </t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L43" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">  Jordan Richardson</t>
         </is>
       </c>
-      <c r="M43" t="n">
+      <c r="M43" s="1" t="n">
         <v>77.90000000000001</v>
       </c>
     </row>
@@ -3055,63 +3069,63 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>STU00277</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="1" t="inlineStr">
         <is>
           <t>Megan</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>Adams</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="1" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="1" t="inlineStr">
         <is>
           <t>Grade 6</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="1" t="inlineStr">
         <is>
           <t>megan.adams182@school.edu.zm</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="1" t="inlineStr">
         <is>
           <t>260960168488</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" s="1" t="inlineStr">
         <is>
           <t>04 Nov 2019</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="J45" s="1" t="n">
         <v>1.94</v>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" s="1" t="inlineStr">
         <is>
           <t>Solwezi</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L45" s="1" t="inlineStr">
         <is>
           <t>Kelly Adams</t>
         </is>
       </c>
-      <c r="M45" t="n">
+      <c r="M45" s="1" t="n">
         <v>82.2</v>
       </c>
     </row>
@@ -3238,120 +3252,120 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="1" t="inlineStr">
         <is>
           <t>STU02155</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="1" t="inlineStr">
         <is>
           <t>Glenn</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>Wright</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="1" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="1" t="inlineStr">
         <is>
           <t>Grade 7</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
+      <c r="G48" s="1" t="inlineStr"/>
+      <c r="H48" s="1" t="inlineStr">
         <is>
           <t>+260-95-2313269</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" s="1" t="inlineStr">
         <is>
           <t>18/11/2019</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="J48" s="1" t="n">
         <v>1.74</v>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K48" s="1" t="inlineStr">
         <is>
           <t>Chipata</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="L48" s="1" t="inlineStr">
         <is>
           <t>John Wright</t>
         </is>
       </c>
-      <c r="M48" t="n">
+      <c r="M48" s="1" t="n">
         <v>91.40000000000001</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="1" t="inlineStr">
         <is>
           <t>STU00389</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="1" t="inlineStr">
         <is>
           <t>Eric</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>Parker</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="1" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="1" t="inlineStr">
         <is>
           <t>Grade 7</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="1" t="inlineStr">
         <is>
           <t>eric.parker190@school.edu.zm</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="1" t="inlineStr">
         <is>
           <t>+260-97-9229532</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" s="1" t="inlineStr">
         <is>
           <t>01-09-2020</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="J49" s="1" t="n">
         <v>1.49</v>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K49" s="1" t="inlineStr">
         <is>
           <t>Kitwe</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L49" s="1" t="inlineStr">
         <is>
           <t>Mark Parker</t>
         </is>
       </c>
-      <c r="M49" t="n">
+      <c r="M49" s="1" t="n">
         <v>77.09999999999999</v>
       </c>
     </row>
@@ -3474,124 +3488,124 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="1" t="inlineStr">
         <is>
           <t>STU00854</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Nicholas   </t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>Matthews</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="1" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="1" t="inlineStr">
         <is>
           <t>Grade 7</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="1" t="inlineStr">
         <is>
           <t>nicholas.matthews24@yahoo.com</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="1" t="inlineStr">
         <is>
           <t>+260-97-6924408</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" s="1" t="inlineStr">
         <is>
           <t>2021-07-17</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="J52" s="1" t="n">
         <v>1.39</v>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K52" s="1" t="inlineStr">
         <is>
           <t>solwezi</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="L52" s="1" t="inlineStr">
         <is>
           <t>Jason Matthews</t>
         </is>
       </c>
-      <c r="M52" t="n">
+      <c r="M52" s="1" t="n">
         <v>82.3</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="1" t="inlineStr">
         <is>
           <t>STU03665</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="1" t="inlineStr">
         <is>
           <t>Maria</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>Ramos</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="1" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="1" t="inlineStr">
         <is>
           <t>Grade 7</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="1" t="inlineStr">
         <is>
           <t>maria_ramos@school.edu.zm</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="1" t="inlineStr">
         <is>
           <t>0953022756</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" s="1" t="inlineStr">
         <is>
           <t>11-12-2022</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="J53" s="1" t="n">
         <v>1.38</v>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K53" s="1" t="inlineStr">
         <is>
           <t>CHINGOLA</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L53" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Kimberly Ramos   </t>
         </is>
       </c>
-      <c r="M53" t="n">
+      <c r="M53" s="1" t="n">
         <v>75.2</v>
       </c>
     </row>
@@ -3657,63 +3671,63 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="1" t="inlineStr">
         <is>
           <t>STU04241</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Grace   </t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Valentine   </t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="1" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="1" t="inlineStr">
         <is>
           <t>Grade 8</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="1" t="inlineStr">
         <is>
           <t>grace_valentine@gmail.com</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="1" t="inlineStr">
         <is>
           <t>(95) 1764359</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I55" s="1" t="inlineStr">
         <is>
           <t>2019/01/12</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="J55" s="1" t="n">
         <v>1.27</v>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K55" s="1" t="inlineStr">
         <is>
           <t>mansa</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L55" s="1" t="inlineStr">
         <is>
           <t>Michael  Valentine</t>
         </is>
       </c>
-      <c r="M55" t="n">
+      <c r="M55" s="1" t="n">
         <v>75.90000000000001</v>
       </c>
     </row>
@@ -3779,63 +3793,63 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="1" t="inlineStr">
         <is>
           <t>STU01942</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="1" t="inlineStr">
         <is>
           <t>Kathy</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>Chambers</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="1" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="1" t="inlineStr">
         <is>
           <t>Grade 8</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="1" t="inlineStr">
         <is>
           <t>kathyc2@yahoo.com</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" s="1" t="inlineStr">
         <is>
           <t>0957699314</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" s="1" t="inlineStr">
         <is>
           <t>07/05/2021</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="J57" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K57" s="1" t="inlineStr">
         <is>
           <t>Mansa</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="L57" s="1" t="inlineStr">
         <is>
           <t>Jacob Chambers</t>
         </is>
       </c>
-      <c r="M57" t="n">
+      <c r="M57" s="1" t="n">
         <v>79.8</v>
       </c>
     </row>
@@ -4261,124 +4275,124 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="1" t="inlineStr">
         <is>
           <t>STU02955</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Jeffrey   </t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>Obrien</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="1" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="1" t="inlineStr">
         <is>
           <t>Grade 10</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="1" t="inlineStr">
         <is>
           <t>jeffrey.obrien701@outlook.com</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H65" s="1" t="inlineStr">
         <is>
           <t>0974117026</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I65" s="1" t="inlineStr">
         <is>
           <t>06/03/2019</t>
         </is>
       </c>
-      <c r="J65" t="n">
+      <c r="J65" s="1" t="n">
         <v>1.05</v>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K65" s="1" t="inlineStr">
         <is>
           <t>Chipata</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="L65" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Melissa Obrien   </t>
         </is>
       </c>
-      <c r="M65" t="n">
+      <c r="M65" s="1" t="n">
         <v>96.7</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>STU02596</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  David</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Jacobson</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Grade 10</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>david_jacobson@school.edu.zm</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>+260-95-8348268</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr">
         <is>
           <t>03 Apr 2023</t>
         </is>
       </c>
-      <c r="J66" t="n">
+      <c r="J66" s="2" t="n">
         <v>3.99</v>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>MONGU</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="L66" s="2" t="inlineStr">
         <is>
           <t>Zachary Jacobson</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4499,63 +4513,63 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="1" t="inlineStr">
         <is>
           <t>STU01881</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="1" t="inlineStr">
         <is>
           <t>John</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="1" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" s="1" t="inlineStr">
         <is>
           <t>Grade 10</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="1" t="inlineStr">
         <is>
           <t>jacqueline.thompson387@yahoo.com</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H69" s="1" t="inlineStr">
         <is>
           <t>+260-97-1667503</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I69" s="1" t="inlineStr">
         <is>
           <t>30 May 2022</t>
         </is>
       </c>
-      <c r="J69" t="n">
+      <c r="J69" s="1" t="n">
         <v>1.92</v>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="K69" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">  Chingola</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="L69" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Jeffrey Short   </t>
         </is>
       </c>
-      <c r="M69" t="n">
+      <c r="M69" s="1" t="n">
         <v>78.90000000000001</v>
       </c>
     </row>
@@ -4804,246 +4818,246 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="1" t="inlineStr">
         <is>
           <t>STU03341</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="1" t="inlineStr">
         <is>
           <t>Michelle</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">  Roberts</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="1" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F74" s="1" t="inlineStr">
         <is>
           <t>Grade 11</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G74" s="1" t="inlineStr">
         <is>
           <t>michelle.roberts370@gmail.com</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H74" s="1" t="inlineStr">
         <is>
           <t>+260-95-4739571</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I74" s="1" t="inlineStr">
         <is>
           <t>2018/03/19</t>
         </is>
       </c>
-      <c r="J74" t="n">
+      <c r="J74" s="1" t="n">
         <v>1.46</v>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="K74" s="1" t="inlineStr">
         <is>
           <t>Chipata</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="L74" s="1" t="inlineStr">
         <is>
           <t>Bryan Roberts</t>
         </is>
       </c>
-      <c r="M74" t="n">
+      <c r="M74" s="1" t="n">
         <v>89</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="1" t="inlineStr">
         <is>
           <t>STU00915</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Joseph   </t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>Roberts</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="1" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" s="1" t="inlineStr">
         <is>
           <t>Grade 11</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" s="1" t="inlineStr">
         <is>
           <t>joseph.roberts878@gmail.com</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H75" s="1" t="inlineStr">
         <is>
           <t>(95) 7735594</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I75" s="1" t="inlineStr">
         <is>
           <t>2022-12-19</t>
         </is>
       </c>
-      <c r="J75" t="n">
+      <c r="J75" s="1" t="n">
         <v>1.62</v>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="K75" s="1" t="inlineStr">
         <is>
           <t>ndola</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="L75" s="1" t="inlineStr">
         <is>
           <t>Jacob Roberts</t>
         </is>
       </c>
-      <c r="M75" t="n">
+      <c r="M75" s="1" t="n">
         <v>87</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="1" t="inlineStr">
         <is>
           <t>STU04454</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="1" t="inlineStr">
         <is>
           <t>Robin</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Watson   </t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" s="1" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" s="1" t="inlineStr">
         <is>
           <t>Grade 11</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G76" s="1" t="inlineStr">
         <is>
           <t>robin_watson@gmail.com</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H76" s="1" t="inlineStr">
         <is>
           <t>260962432072</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I76" s="1" t="inlineStr">
         <is>
           <t>2022/04/30</t>
         </is>
       </c>
-      <c r="J76" t="n">
+      <c r="J76" s="1" t="n">
         <v>1.44</v>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="K76" s="1" t="inlineStr">
         <is>
           <t>Kabwe</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="L76" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">  Anthony Watson</t>
         </is>
       </c>
-      <c r="M76" t="n">
+      <c r="M76" s="1" t="n">
         <v>91.59999999999999</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="1" t="inlineStr">
         <is>
           <t>STU01032</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="1" t="inlineStr">
         <is>
           <t>Loretta</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>Foster</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="1" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F77" s="1" t="inlineStr">
         <is>
           <t>Grade 12</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G77" s="1" t="inlineStr">
         <is>
           <t>loretta_foster@gmail.com</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H77" s="1" t="inlineStr">
         <is>
           <t>260974160580</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I77" s="1" t="inlineStr">
         <is>
           <t>10-23-2023</t>
         </is>
       </c>
-      <c r="J77" t="n">
+      <c r="J77" s="1" t="n">
         <v>1.81</v>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="K77" s="1" t="inlineStr">
         <is>
           <t>Solwezi</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="L77" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Juan Foster   </t>
         </is>
       </c>
-      <c r="M77" t="n">
+      <c r="M77" s="1" t="n">
         <v>99.7</v>
       </c>
     </row>
@@ -5530,61 +5544,61 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="1" t="inlineStr">
         <is>
           <t>STU01514</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="1" t="inlineStr">
         <is>
           <t>Henry</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>Lee</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" s="1" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr">
+      <c r="E86" s="1" t="inlineStr"/>
+      <c r="F86" s="1" t="inlineStr">
         <is>
           <t>Grade 7</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G86" s="1" t="inlineStr">
         <is>
           <t>henry_lee@gmail.com</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H86" s="1" t="inlineStr">
         <is>
           <t>0978851786</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I86" s="1" t="inlineStr">
         <is>
           <t>2022-05-28</t>
         </is>
       </c>
-      <c r="J86" t="n">
+      <c r="J86" s="1" t="n">
         <v>1.98</v>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="K86" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">  LUSAKA</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="L86" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">  Denise Lee</t>
         </is>
       </c>
-      <c r="M86" t="n">
+      <c r="M86" s="1" t="n">
         <v>75.59999999999999</v>
       </c>
     </row>
